--- a/OECD_salaries/impacts.xlsx
+++ b/OECD_salaries/impacts.xlsx
@@ -1068,139 +1068,139 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>41541.8631259246</v>
+        <v>41541.86515700947</v>
       </c>
       <c r="C5" t="n">
-        <v>2317.732567524915</v>
+        <v>2317.732680844619</v>
       </c>
       <c r="D5" t="n">
-        <v>18413.40165933065</v>
+        <v>18413.40255960759</v>
       </c>
       <c r="E5" t="n">
-        <v>3764.068624245475</v>
+        <v>3764.068808280145</v>
       </c>
       <c r="F5" t="n">
-        <v>2780.229483091842</v>
+        <v>2780.22961902417</v>
       </c>
       <c r="G5" t="n">
-        <v>87322.51091368127</v>
+        <v>87322.51518309575</v>
       </c>
       <c r="H5" t="n">
-        <v>4721.642977177402</v>
+        <v>4721.643208030258</v>
       </c>
       <c r="I5" t="n">
-        <v>4146.094660267616</v>
+        <v>4146.094862980484</v>
       </c>
       <c r="J5" t="n">
-        <v>11639.77505709287</v>
+        <v>11639.77562619039</v>
       </c>
       <c r="K5" t="n">
-        <v>25702.05812998429</v>
+        <v>25702.05938662175</v>
       </c>
       <c r="L5" t="n">
-        <v>12758.40692563009</v>
+        <v>12758.4075494203</v>
       </c>
       <c r="M5" t="n">
-        <v>4179.908296776224</v>
+        <v>4179.908501142321</v>
       </c>
       <c r="N5" t="n">
-        <v>8178.463819568418</v>
+        <v>8178.464219433832</v>
       </c>
       <c r="O5" t="n">
-        <v>4978.05338661452</v>
+        <v>4978.053630003916</v>
       </c>
       <c r="P5" t="n">
-        <v>5683.532299995476</v>
+        <v>5683.532577877505</v>
       </c>
       <c r="Q5" t="n">
-        <v>8589.035838923985</v>
+        <v>8589.036258863276</v>
       </c>
       <c r="R5" t="n">
-        <v>3802.120419591251</v>
+        <v>3802.120605486368</v>
       </c>
       <c r="S5" t="n">
-        <v>3610.901304874991</v>
+        <v>3610.901481420923</v>
       </c>
       <c r="T5" t="n">
-        <v>5420.623706646658</v>
+        <v>5420.623971674411</v>
       </c>
       <c r="U5" t="n">
-        <v>26851.72823481118</v>
+        <v>26851.72954765885</v>
       </c>
       <c r="V5" t="n">
-        <v>6808.701608370286</v>
+        <v>6808.701941264619</v>
       </c>
       <c r="W5" t="n">
-        <v>20131.66971142565</v>
+        <v>20131.67069571299</v>
       </c>
       <c r="X5" t="n">
-        <v>39646.89598781936</v>
+        <v>39646.89792625459</v>
       </c>
       <c r="Y5" t="n">
-        <v>9770.532872626147</v>
+        <v>9770.533350331771</v>
       </c>
       <c r="Z5" t="n">
-        <v>30637.03185232735</v>
+        <v>30637.03335024794</v>
       </c>
       <c r="AA5" t="n">
-        <v>158994.2536657857</v>
+        <v>158994.2614394097</v>
       </c>
       <c r="AB5" t="n">
-        <v>35175.78991851605</v>
+        <v>35175.7916383478</v>
       </c>
       <c r="AC5" t="n">
-        <v>1302.966745238898</v>
+        <v>1302.966808944178</v>
       </c>
       <c r="AD5" t="n">
-        <v>5751.831467789641</v>
+        <v>5751.831749010964</v>
       </c>
       <c r="AE5" t="n">
-        <v>15062.98491209448</v>
+        <v>15062.98564856123</v>
       </c>
       <c r="AF5" t="n">
-        <v>7615.346352248091</v>
+        <v>7615.346724581292</v>
       </c>
       <c r="AG5" t="n">
-        <v>77455.9682260839</v>
+        <v>77455.97201309858</v>
       </c>
       <c r="AH5" t="n">
-        <v>25085.34866782964</v>
+        <v>25085.34989431465</v>
       </c>
       <c r="AI5" t="n">
-        <v>48324.85022395398</v>
+        <v>48324.85258667594</v>
       </c>
       <c r="AJ5" t="n">
-        <v>17470.72126666179</v>
+        <v>17470.72212084875</v>
       </c>
       <c r="AK5" t="n">
-        <v>183768.4093408731</v>
+        <v>183768.4183257671</v>
       </c>
       <c r="AL5" t="n">
-        <v>289752.5687037486</v>
+        <v>289752.5828704715</v>
       </c>
       <c r="AM5" t="n">
-        <v>48663.02895851135</v>
+        <v>48663.03133776773</v>
       </c>
       <c r="AN5" t="n">
-        <v>44315.63891113007</v>
+        <v>44315.64107783175</v>
       </c>
       <c r="AO5" t="n">
-        <v>22101.46013204492</v>
+        <v>22101.46121264019</v>
       </c>
       <c r="AP5" t="n">
-        <v>18623.44730367418</v>
+        <v>18623.44821422076</v>
       </c>
       <c r="AQ5" t="n">
-        <v>50833.91937525927</v>
+        <v>50833.92186065586</v>
       </c>
       <c r="AR5" t="n">
-        <v>26107.82362922711</v>
+        <v>26107.82490570346</v>
       </c>
       <c r="AS5" t="n">
-        <v>19322.87634961276</v>
+        <v>19322.87729435618</v>
       </c>
       <c r="AT5" t="n">
-        <v>3747.094976326749</v>
+        <v>3747.095159531646</v>
       </c>
     </row>
     <row r="6">
@@ -1210,139 +1210,139 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>110334.4875106745</v>
+        <v>110334.4895417594</v>
       </c>
       <c r="C6" t="n">
-        <v>5691.227266508884</v>
+        <v>5691.22737982859</v>
       </c>
       <c r="D6" t="n">
-        <v>100650.7028390513</v>
+        <v>100650.7037393282</v>
       </c>
       <c r="E6" t="n">
-        <v>32456.02127663677</v>
+        <v>32456.02146067143</v>
       </c>
       <c r="F6" t="n">
-        <v>22473.3287285206</v>
+        <v>22473.32886445292</v>
       </c>
       <c r="G6" t="n">
-        <v>175336.116007759</v>
+        <v>175336.1202771734</v>
       </c>
       <c r="H6" t="n">
-        <v>9919.63145378001</v>
+        <v>9919.631684632865</v>
       </c>
       <c r="I6" t="n">
-        <v>26858.46756151594</v>
+        <v>26858.46776422882</v>
       </c>
       <c r="J6" t="n">
-        <v>40609.97580559005</v>
+        <v>40609.97637468755</v>
       </c>
       <c r="K6" t="n">
-        <v>69859.3694866218</v>
+        <v>69859.37074325926</v>
       </c>
       <c r="L6" t="n">
-        <v>47849.75127157864</v>
+        <v>47849.75189536886</v>
       </c>
       <c r="M6" t="n">
-        <v>14465.90282415055</v>
+        <v>14465.90302851665</v>
       </c>
       <c r="N6" t="n">
-        <v>31324.6282995366</v>
+        <v>31324.62869940202</v>
       </c>
       <c r="O6" t="n">
-        <v>21615.21876855899</v>
+        <v>21615.21901194838</v>
       </c>
       <c r="P6" t="n">
-        <v>59797.35999713039</v>
+        <v>59797.36027501243</v>
       </c>
       <c r="Q6" t="n">
-        <v>37619.62386685595</v>
+        <v>37619.62428679525</v>
       </c>
       <c r="R6" t="n">
-        <v>15298.92092897466</v>
+        <v>15298.92111486978</v>
       </c>
       <c r="S6" t="n">
-        <v>11907.8961755224</v>
+        <v>11907.89635206833</v>
       </c>
       <c r="T6" t="n">
-        <v>33906.31304101213</v>
+        <v>33906.31330603988</v>
       </c>
       <c r="U6" t="n">
-        <v>104008.4724263591</v>
+        <v>104008.4737392067</v>
       </c>
       <c r="V6" t="n">
-        <v>33768.33025476149</v>
+        <v>33768.33058765582</v>
       </c>
       <c r="W6" t="n">
-        <v>48451.45801094493</v>
+        <v>48451.45899523226</v>
       </c>
       <c r="X6" t="n">
-        <v>82608.88610490295</v>
+        <v>82608.8880433382</v>
       </c>
       <c r="Y6" t="n">
-        <v>22891.7289178737</v>
+        <v>22891.72939557932</v>
       </c>
       <c r="Z6" t="n">
-        <v>291262.5690111644</v>
+        <v>291262.570509085</v>
       </c>
       <c r="AA6" t="n">
-        <v>414704.1615867753</v>
+        <v>414704.1693603994</v>
       </c>
       <c r="AB6" t="n">
-        <v>109106.1055813702</v>
+        <v>109106.1073012019</v>
       </c>
       <c r="AC6" t="n">
-        <v>5935.665885960423</v>
+        <v>5935.665949665703</v>
       </c>
       <c r="AD6" t="n">
-        <v>23538.12704076388</v>
+        <v>23538.1273219852</v>
       </c>
       <c r="AE6" t="n">
-        <v>44986.28231468578</v>
+        <v>44986.28305115253</v>
       </c>
       <c r="AF6" t="n">
-        <v>18667.13700593514</v>
+        <v>18667.13737826834</v>
       </c>
       <c r="AG6" t="n">
-        <v>145133.2598049275</v>
+        <v>145133.2635919421</v>
       </c>
       <c r="AH6" t="n">
-        <v>55112.19894732081</v>
+        <v>55112.20017380582</v>
       </c>
       <c r="AI6" t="n">
-        <v>93537.43782578493</v>
+        <v>93537.44018850691</v>
       </c>
       <c r="AJ6" t="n">
-        <v>61126.59228562488</v>
+        <v>61126.59313981185</v>
       </c>
       <c r="AK6" t="n">
-        <v>380727.3589904523</v>
+        <v>380727.3679753464</v>
       </c>
       <c r="AL6" t="n">
-        <v>522370.9520801206</v>
+        <v>522370.9662468435</v>
       </c>
       <c r="AM6" t="n">
-        <v>150956.6013221141</v>
+        <v>150956.6037013705</v>
       </c>
       <c r="AN6" t="n">
-        <v>121900.1008145486</v>
+        <v>121900.1029812503</v>
       </c>
       <c r="AO6" t="n">
-        <v>209823.5484223097</v>
+        <v>209823.549502905</v>
       </c>
       <c r="AP6" t="n">
-        <v>120061.4435539704</v>
+        <v>120061.444464517</v>
       </c>
       <c r="AQ6" t="n">
-        <v>210747.5110652954</v>
+        <v>210747.513550692</v>
       </c>
       <c r="AR6" t="n">
-        <v>48550.11954952309</v>
+        <v>48550.12082599945</v>
       </c>
       <c r="AS6" t="n">
-        <v>50761.5707390273</v>
+        <v>50761.57168377072</v>
       </c>
       <c r="AT6" t="n">
-        <v>6310.49497632675</v>
+        <v>6310.495159531647</v>
       </c>
     </row>
     <row r="8">
@@ -1591,139 +1591,139 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3277.180764126218</v>
+        <v>3198.357093163043</v>
       </c>
       <c r="C10" t="n">
-        <v>214.281175529077</v>
+        <v>209.1269962653388</v>
       </c>
       <c r="D10" t="n">
-        <v>8311.609387954128</v>
+        <v>8111.794456286868</v>
       </c>
       <c r="E10" t="n">
-        <v>2529.487616757284</v>
+        <v>2468.671026767043</v>
       </c>
       <c r="F10" t="n">
-        <v>1573.359215156578</v>
+        <v>1535.539227952938</v>
       </c>
       <c r="G10" t="n">
-        <v>9287.601709847442</v>
+        <v>9064.310618574153</v>
       </c>
       <c r="H10" t="n">
-        <v>1046.587257127467</v>
+        <v>1021.456842753261</v>
       </c>
       <c r="I10" t="n">
-        <v>2056.020994421623</v>
+        <v>2006.607401145615</v>
       </c>
       <c r="J10" t="n">
-        <v>3724.064949948222</v>
+        <v>3634.539859164653</v>
       </c>
       <c r="K10" t="n">
-        <v>514.4400267228299</v>
+        <v>502.0636170935526</v>
       </c>
       <c r="L10" t="n">
-        <v>2102.64377324294</v>
+        <v>2052.074228654965</v>
       </c>
       <c r="M10" t="n">
-        <v>1619.757820748389</v>
+        <v>1580.862963611087</v>
       </c>
       <c r="N10" t="n">
-        <v>2270.910296500149</v>
+        <v>2216.30092583392</v>
       </c>
       <c r="O10" t="n">
-        <v>754.0022792022792</v>
+        <v>735.876419392453</v>
       </c>
       <c r="P10" t="n">
-        <v>3231.907350038808</v>
+        <v>3154.179401263998</v>
       </c>
       <c r="Q10" t="n">
-        <v>2972.588319991182</v>
+        <v>2901.109425162242</v>
       </c>
       <c r="R10" t="n">
-        <v>2421.916363826141</v>
+        <v>2363.67204241217</v>
       </c>
       <c r="S10" t="n">
-        <v>1173.133934339295</v>
+        <v>1144.964180687461</v>
       </c>
       <c r="T10" t="n">
-        <v>5853.05591066426</v>
+        <v>5712.389686089209</v>
       </c>
       <c r="U10" t="n">
-        <v>7401.456424224044</v>
+        <v>7223.456692510277</v>
       </c>
       <c r="V10" t="n">
-        <v>4584.721287936674</v>
+        <v>4474.520661068124</v>
       </c>
       <c r="W10" t="n">
-        <v>2751.487896186441</v>
+        <v>2685.34066101695</v>
       </c>
       <c r="X10" t="n">
-        <v>5702.120162563021</v>
+        <v>5565.026577098725</v>
       </c>
       <c r="Y10" t="n">
-        <v>664.6131147540984</v>
+        <v>648.6491803278689</v>
       </c>
       <c r="Z10" t="n">
-        <v>64859.86510253217</v>
+        <v>63300.49473378468</v>
       </c>
       <c r="AA10" t="n">
-        <v>65828.72987415432</v>
+        <v>64246.10844323648</v>
       </c>
       <c r="AB10" t="n">
-        <v>7680.614350563101</v>
+        <v>7495.978531912535</v>
       </c>
       <c r="AC10" t="n">
-        <v>734.2300112247981</v>
+        <v>716.532983637698</v>
       </c>
       <c r="AD10" t="n">
-        <v>2674.452359400213</v>
+        <v>2610.153189814633</v>
       </c>
       <c r="AE10" t="n">
-        <v>2199.225787187113</v>
+        <v>2146.372879390436</v>
       </c>
       <c r="AF10" t="n">
-        <v>1113.982196726355</v>
+        <v>1087.194896805074</v>
       </c>
       <c r="AG10" t="n">
-        <v>20195.40982444579</v>
+        <v>19709.88015355268</v>
       </c>
       <c r="AH10" t="n">
-        <v>4786.262403420898</v>
+        <v>4671.175329035008</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>7345.153085135869</v>
+        <v>7168.561579710511</v>
       </c>
       <c r="AK10" t="n">
-        <v>27059.7935408925</v>
+        <v>26409.23135762704</v>
       </c>
       <c r="AL10" t="n">
-        <v>8264.812333552432</v>
+        <v>8066.124703000581</v>
       </c>
       <c r="AM10" t="n">
-        <v>8949.355840846036</v>
+        <v>8734.200124054923</v>
       </c>
       <c r="AN10" t="n">
-        <v>6905.436149091058</v>
+        <v>6739.412748888956</v>
       </c>
       <c r="AO10" t="n">
-        <v>79215.08285439869</v>
+        <v>77310.64849591577</v>
       </c>
       <c r="AP10" t="n">
-        <v>61494.33426973547</v>
+        <v>60015.92005197268</v>
       </c>
       <c r="AQ10" t="n">
-        <v>66495.97249975767</v>
+        <v>64897.36517980032</v>
       </c>
       <c r="AR10" t="n">
-        <v>5852.792956127296</v>
+        <v>5712.085039791108</v>
       </c>
       <c r="AS10" t="n">
-        <v>9395.501375370564</v>
+        <v>9169.592020051658</v>
       </c>
       <c r="AT10" t="n">
-        <v>2626.5</v>
+        <v>2563.4</v>
       </c>
     </row>
     <row r="11">
@@ -1733,136 +1733,136 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4098.454014942976</v>
+        <v>3999.876849390223</v>
       </c>
       <c r="C11" t="n">
-        <v>205.5808269913358</v>
+        <v>200.635920221599</v>
       </c>
       <c r="D11" t="n">
-        <v>4183.990791299291</v>
+        <v>4083.405718657217</v>
       </c>
       <c r="E11" t="n">
-        <v>3027.203213562759</v>
+        <v>2954.420024020048</v>
       </c>
       <c r="F11" t="n">
-        <v>6335.040481820983</v>
+        <v>6182.760476308595</v>
       </c>
       <c r="G11" t="n">
-        <v>3922.684045373559</v>
+        <v>3828.375479117634</v>
       </c>
       <c r="H11" t="n">
-        <v>448.4519047686809</v>
+        <v>437.6837799735532</v>
       </c>
       <c r="I11" t="n">
-        <v>2991.006319367158</v>
+        <v>2919.121659554743</v>
       </c>
       <c r="J11" t="n">
-        <v>2939.981228442704</v>
+        <v>2869.305209115495</v>
       </c>
       <c r="K11" t="n">
-        <v>616.1679452819342</v>
+        <v>601.3441631205433</v>
       </c>
       <c r="L11" t="n">
-        <v>2225.761696688459</v>
+        <v>2172.231109722081</v>
       </c>
       <c r="M11" t="n">
-        <v>699.8183943085808</v>
+        <v>683.0138225880308</v>
       </c>
       <c r="N11" t="n">
-        <v>3355.359531600313</v>
+        <v>3274.672032555539</v>
       </c>
       <c r="O11" t="n">
-        <v>2848.346920307064</v>
+        <v>2779.874001336768</v>
       </c>
       <c r="P11" t="n">
-        <v>2061.175796350387</v>
+        <v>2011.604150457545</v>
       </c>
       <c r="Q11" t="n">
-        <v>6450.942872398271</v>
+        <v>6295.82342177585</v>
       </c>
       <c r="R11" t="n">
-        <v>1000.313554603661</v>
+        <v>976.2571565135783</v>
       </c>
       <c r="S11" t="n">
-        <v>892.414998410221</v>
+        <v>870.9859783089687</v>
       </c>
       <c r="T11" t="n">
-        <v>2789.210514515538</v>
+        <v>2722.177545992706</v>
       </c>
       <c r="U11" t="n">
-        <v>1704.884198608184</v>
+        <v>1663.882953371898</v>
       </c>
       <c r="V11" t="n">
-        <v>2013.634673156045</v>
+        <v>1965.233954916112</v>
       </c>
       <c r="W11" t="n">
-        <v>3051.168726893379</v>
+        <v>2977.817004867145</v>
       </c>
       <c r="X11" t="n">
-        <v>4729.425999524168</v>
+        <v>4615.718475133558</v>
       </c>
       <c r="Y11" t="n">
-        <v>1587.703371875152</v>
+        <v>1549.566910294348</v>
       </c>
       <c r="Z11" t="n">
-        <v>11597.54579842751</v>
+        <v>11318.71590509253</v>
       </c>
       <c r="AA11" t="n">
-        <v>43336.63081630754</v>
+        <v>42294.75319228565</v>
       </c>
       <c r="AB11" t="n">
-        <v>11870.81623735261</v>
+        <v>11585.45132069418</v>
       </c>
       <c r="AC11" t="n">
-        <v>199.2899662961496</v>
+        <v>194.4865123682832</v>
       </c>
       <c r="AD11" t="n">
-        <v>1135.546692287425</v>
+        <v>1108.245884672326</v>
       </c>
       <c r="AE11" t="n">
-        <v>6439.160068268704</v>
+        <v>6284.410912743593</v>
       </c>
       <c r="AF11" t="n">
-        <v>3589.371268338627</v>
+        <v>3503.059687259174</v>
       </c>
       <c r="AG11" t="n">
-        <v>4890.361187601065</v>
+        <v>4772.78915125198</v>
       </c>
       <c r="AH11" t="n">
-        <v>4716.526918293299</v>
+        <v>4603.116653970827</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>10502.75330014484</v>
+        <v>10250.24705624681</v>
       </c>
       <c r="AK11" t="n">
-        <v>36800.15771102796</v>
+        <v>35915.42106627786</v>
       </c>
       <c r="AL11" t="n">
-        <v>1489.691162710847</v>
+        <v>1453.878709211878</v>
       </c>
       <c r="AM11" t="n">
-        <v>31730.41270413978</v>
+        <v>30967.56677300831</v>
       </c>
       <c r="AN11" t="n">
-        <v>24060.5289078202</v>
+        <v>23482.0555523808</v>
       </c>
       <c r="AO11" t="n">
-        <v>8047.165217547928</v>
+        <v>7853.700824449263</v>
       </c>
       <c r="AP11" t="n">
-        <v>2898.626830067474</v>
+        <v>2828.939578901159</v>
       </c>
       <c r="AQ11" t="n">
-        <v>12748.97293710503</v>
+        <v>12442.47916473005</v>
       </c>
       <c r="AR11" t="n">
-        <v>1280.837533620744</v>
+        <v>1250.044716948102</v>
       </c>
       <c r="AS11" t="n">
-        <v>4004.6536100943</v>
+        <v>3908.36404776147</v>
       </c>
       <c r="AT11" t="n">
         <v>0</v>
@@ -1875,139 +1875,139 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4453.931118331115</v>
+        <v>4346.804130305072</v>
       </c>
       <c r="C12" t="n">
-        <v>288.4628327416302</v>
+        <v>281.5243501719499</v>
       </c>
       <c r="D12" t="n">
-        <v>2797.836283223452</v>
+        <v>2730.575139199931</v>
       </c>
       <c r="E12" t="n">
-        <v>728.9767225827698</v>
+        <v>711.4499356679235</v>
       </c>
       <c r="F12" t="n">
-        <v>1116.490894987763</v>
+        <v>1089.653039313986</v>
       </c>
       <c r="G12" t="n">
-        <v>13106.5568874278</v>
+        <v>12791.45168878366</v>
       </c>
       <c r="H12" t="n">
-        <v>1358.033245196017</v>
+        <v>1325.424525635364</v>
       </c>
       <c r="I12" t="n">
-        <v>921.3239447461849</v>
+        <v>899.1812543673479</v>
       </c>
       <c r="J12" t="n">
-        <v>2677.509871607419</v>
+        <v>2613.143690632277</v>
       </c>
       <c r="K12" t="n">
-        <v>658.0779247177172</v>
+        <v>642.2459027379225</v>
       </c>
       <c r="L12" t="n">
-        <v>1573.708826315847</v>
+        <v>1535.860484251542</v>
       </c>
       <c r="M12" t="n">
-        <v>942.6036384248773</v>
+        <v>919.9691676861107</v>
       </c>
       <c r="N12" t="n">
-        <v>1987.985710032953</v>
+        <v>1940.18002027646</v>
       </c>
       <c r="O12" t="n">
-        <v>1077.869109352431</v>
+        <v>1051.95769485423</v>
       </c>
       <c r="P12" t="n">
-        <v>555.9283146155535</v>
+        <v>542.5581659237832</v>
       </c>
       <c r="Q12" t="n">
-        <v>2788.060891593895</v>
+        <v>2721.019278585693</v>
       </c>
       <c r="R12" t="n">
-        <v>1131.76968172825</v>
+        <v>1104.551967978978</v>
       </c>
       <c r="S12" t="n">
-        <v>898.9391283022923</v>
+        <v>877.3534911228585</v>
       </c>
       <c r="T12" t="n">
-        <v>1644.561720574897</v>
+        <v>1605.038122555272</v>
       </c>
       <c r="U12" t="n">
-        <v>3169.145953215302</v>
+        <v>3092.930411591372</v>
       </c>
       <c r="V12" t="n">
-        <v>1666.426397564844</v>
+        <v>1626.371428561532</v>
       </c>
       <c r="W12" t="n">
-        <v>4124.930785116159</v>
+        <v>4025.765447880006</v>
       </c>
       <c r="X12" t="n">
-        <v>9626.612374177472</v>
+        <v>9395.164395295826</v>
       </c>
       <c r="Y12" t="n">
-        <v>1677.159017842702</v>
+        <v>1636.873921447081</v>
       </c>
       <c r="Z12" t="n">
-        <v>8987.715320051693</v>
+        <v>8771.631781881748</v>
       </c>
       <c r="AA12" t="n">
-        <v>67876.38848354371</v>
+        <v>66244.54150635489</v>
       </c>
       <c r="AB12" t="n">
-        <v>9302.503429084119</v>
+        <v>9078.879139620476</v>
       </c>
       <c r="AC12" t="n">
-        <v>262.556546362844</v>
+        <v>256.2282007831769</v>
       </c>
       <c r="AD12" t="n">
-        <v>1232.098744105212</v>
+        <v>1202.476691359213</v>
       </c>
       <c r="AE12" t="n">
-        <v>4348.44709976091</v>
+        <v>4243.943224520442</v>
       </c>
       <c r="AF12" t="n">
-        <v>3240.892519219652</v>
+        <v>3162.960764198509</v>
       </c>
       <c r="AG12" t="n">
-        <v>28710.40842661805</v>
+        <v>28020.16605924141</v>
       </c>
       <c r="AH12" t="n">
-        <v>7938.920707076195</v>
+        <v>7748.027423796818</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>7142.585644786859</v>
+        <v>6970.864588244309</v>
       </c>
       <c r="AK12" t="n">
-        <v>59583.18564873701</v>
+        <v>58150.71018108803</v>
       </c>
       <c r="AL12" t="n">
-        <v>12150.33998365871</v>
+        <v>11858.24412321339</v>
       </c>
       <c r="AM12" t="n">
-        <v>19352.151938674</v>
+        <v>18886.89858057952</v>
       </c>
       <c r="AN12" t="n">
-        <v>17687.51747875801</v>
+        <v>17262.26758846836</v>
       </c>
       <c r="AO12" t="n">
-        <v>10273.82080798406</v>
+        <v>10026.82518795206</v>
       </c>
       <c r="AP12" t="n">
-        <v>11822.18657800252</v>
+        <v>11537.96439331907</v>
       </c>
       <c r="AQ12" t="n">
-        <v>25190.67406754579</v>
+        <v>24585.07474302515</v>
       </c>
       <c r="AR12" t="n">
-        <v>8298.775104109867</v>
+        <v>8099.263342096499</v>
       </c>
       <c r="AS12" t="n">
-        <v>8236.014340880723</v>
+        <v>8037.984568609174</v>
       </c>
       <c r="AT12" t="n">
-        <v>3839.332509683314</v>
+        <v>3747.095159531646</v>
       </c>
     </row>
     <row r="13">
@@ -2017,139 +2017,139 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>110334.4875106745</v>
+        <v>110334.4895417594</v>
       </c>
       <c r="C13" t="n">
-        <v>5691.227266508884</v>
+        <v>5691.22737982859</v>
       </c>
       <c r="D13" t="n">
-        <v>100650.7028390513</v>
+        <v>100650.7037393282</v>
       </c>
       <c r="E13" t="n">
-        <v>32456.02127663677</v>
+        <v>32456.02146067143</v>
       </c>
       <c r="F13" t="n">
-        <v>22473.3287285206</v>
+        <v>22473.32886445292</v>
       </c>
       <c r="G13" t="n">
-        <v>175336.116007759</v>
+        <v>175336.1202771734</v>
       </c>
       <c r="H13" t="n">
-        <v>9919.63145378001</v>
+        <v>9919.631684632865</v>
       </c>
       <c r="I13" t="n">
-        <v>26858.46756151594</v>
+        <v>26858.46776422882</v>
       </c>
       <c r="J13" t="n">
-        <v>40609.97580559005</v>
+        <v>40609.97637468755</v>
       </c>
       <c r="K13" t="n">
-        <v>69859.3694866218</v>
+        <v>69859.37074325926</v>
       </c>
       <c r="L13" t="n">
-        <v>47849.75127157864</v>
+        <v>47849.75189536886</v>
       </c>
       <c r="M13" t="n">
-        <v>14465.90282415055</v>
+        <v>14465.90302851665</v>
       </c>
       <c r="N13" t="n">
-        <v>31324.6282995366</v>
+        <v>31324.62869940202</v>
       </c>
       <c r="O13" t="n">
-        <v>21615.21876855899</v>
+        <v>21615.21901194838</v>
       </c>
       <c r="P13" t="n">
-        <v>59797.35999713039</v>
+        <v>59797.36027501243</v>
       </c>
       <c r="Q13" t="n">
-        <v>37619.62386685595</v>
+        <v>37619.62428679525</v>
       </c>
       <c r="R13" t="n">
-        <v>15298.92092897466</v>
+        <v>15298.92111486978</v>
       </c>
       <c r="S13" t="n">
-        <v>11907.8961755224</v>
+        <v>11907.89635206833</v>
       </c>
       <c r="T13" t="n">
-        <v>33906.31304101213</v>
+        <v>33906.31330603988</v>
       </c>
       <c r="U13" t="n">
-        <v>104008.4724263591</v>
+        <v>104008.4737392067</v>
       </c>
       <c r="V13" t="n">
-        <v>33768.33025476149</v>
+        <v>33768.33058765582</v>
       </c>
       <c r="W13" t="n">
-        <v>48451.45801094493</v>
+        <v>48451.45899523226</v>
       </c>
       <c r="X13" t="n">
-        <v>82608.88610490295</v>
+        <v>82608.8880433382</v>
       </c>
       <c r="Y13" t="n">
-        <v>22891.7289178737</v>
+        <v>22891.72939557932</v>
       </c>
       <c r="Z13" t="n">
-        <v>291262.5690111644</v>
+        <v>291262.570509085</v>
       </c>
       <c r="AA13" t="n">
-        <v>414704.1615867753</v>
+        <v>414704.1693603994</v>
       </c>
       <c r="AB13" t="n">
-        <v>109106.1055813702</v>
+        <v>109106.1073012019</v>
       </c>
       <c r="AC13" t="n">
-        <v>5935.665885960423</v>
+        <v>5935.665949665703</v>
       </c>
       <c r="AD13" t="n">
-        <v>23538.12704076388</v>
+        <v>23538.1273219852</v>
       </c>
       <c r="AE13" t="n">
-        <v>44986.28231468578</v>
+        <v>44986.28305115253</v>
       </c>
       <c r="AF13" t="n">
-        <v>18667.13700593514</v>
+        <v>18667.13737826834</v>
       </c>
       <c r="AG13" t="n">
-        <v>145133.2598049275</v>
+        <v>145133.2635919421</v>
       </c>
       <c r="AH13" t="n">
-        <v>55112.19894732081</v>
+        <v>55112.20017380582</v>
       </c>
       <c r="AI13" t="n">
-        <v>93537.43782578493</v>
+        <v>93537.44018850691</v>
       </c>
       <c r="AJ13" t="n">
-        <v>61126.59228562488</v>
+        <v>61126.59313981185</v>
       </c>
       <c r="AK13" t="n">
-        <v>380727.3589904523</v>
+        <v>380727.3679753464</v>
       </c>
       <c r="AL13" t="n">
-        <v>522370.9520801206</v>
+        <v>522370.9662468435</v>
       </c>
       <c r="AM13" t="n">
-        <v>150956.6013221141</v>
+        <v>150956.6037013705</v>
       </c>
       <c r="AN13" t="n">
-        <v>121900.1008145486</v>
+        <v>121900.1029812503</v>
       </c>
       <c r="AO13" t="n">
-        <v>209823.5484223097</v>
+        <v>209823.549502905</v>
       </c>
       <c r="AP13" t="n">
-        <v>120061.4435539704</v>
+        <v>120061.444464517</v>
       </c>
       <c r="AQ13" t="n">
-        <v>210747.5110652954</v>
+        <v>210747.513550692</v>
       </c>
       <c r="AR13" t="n">
-        <v>48550.11954952309</v>
+        <v>48550.12082599945</v>
       </c>
       <c r="AS13" t="n">
-        <v>50761.5707390273</v>
+        <v>50761.57168377072</v>
       </c>
       <c r="AT13" t="n">
-        <v>6310.49497632675</v>
+        <v>6310.495159531647</v>
       </c>
     </row>
     <row r="15">
@@ -2682,139 +2682,139 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>16523.37429349632</v>
+        <v>16523.37510136513</v>
       </c>
       <c r="C19" t="n">
-        <v>1198.161530327881</v>
+        <v>1198.161588908975</v>
       </c>
       <c r="D19" t="n">
-        <v>8943.913884356163</v>
+        <v>8943.914321646324</v>
       </c>
       <c r="E19" t="n">
-        <v>2282.868526346899</v>
+        <v>2282.868637962015</v>
       </c>
       <c r="F19" t="n">
-        <v>1668.340985956564</v>
+        <v>1668.341067525901</v>
       </c>
       <c r="G19" t="n">
-        <v>23705.065876191</v>
+        <v>23705.06703519056</v>
       </c>
       <c r="H19" t="n">
-        <v>1742.617069700059</v>
+        <v>1742.617154900937</v>
       </c>
       <c r="I19" t="n">
-        <v>1279.331616564897</v>
+        <v>1279.331679114598</v>
       </c>
       <c r="J19" t="n">
-        <v>4038.805069085376</v>
+        <v>4038.805266552586</v>
       </c>
       <c r="K19" t="n">
-        <v>6227.875792589915</v>
+        <v>6227.876097086233</v>
       </c>
       <c r="L19" t="n">
-        <v>4191.575858503719</v>
+        <v>4191.576063440276</v>
       </c>
       <c r="M19" t="n">
-        <v>1623.386478333998</v>
+        <v>1623.386557705395</v>
       </c>
       <c r="N19" t="n">
-        <v>2829.409919096026</v>
+        <v>2829.410057432905</v>
       </c>
       <c r="O19" t="n">
-        <v>1707.793003400753</v>
+        <v>1707.793086898995</v>
       </c>
       <c r="P19" t="n">
-        <v>932.1417288629536</v>
+        <v>932.1417744376802</v>
       </c>
       <c r="Q19" t="n">
-        <v>3550.875250946642</v>
+        <v>3550.875424557751</v>
       </c>
       <c r="R19" t="n">
-        <v>1628.96521077689</v>
+        <v>1628.965290421047</v>
       </c>
       <c r="S19" t="n">
-        <v>1259.324242626037</v>
+        <v>1259.324304197527</v>
       </c>
       <c r="T19" t="n">
-        <v>2210.052858933022</v>
+        <v>2210.052966987993</v>
       </c>
       <c r="U19" t="n">
-        <v>5079.132096921989</v>
+        <v>5079.132345253371</v>
       </c>
       <c r="V19" t="n">
-        <v>2640.425767834243</v>
+        <v>2640.425896931218</v>
       </c>
       <c r="W19" t="n">
-        <v>8789.691724852963</v>
+        <v>8789.692154602822</v>
       </c>
       <c r="X19" t="n">
-        <v>28869.59359117514</v>
+        <v>28869.59500268129</v>
       </c>
       <c r="Y19" t="n">
-        <v>5640.892735365544</v>
+        <v>5640.893011162803</v>
       </c>
       <c r="Z19" t="n">
-        <v>13726.25733291569</v>
+        <v>13726.25800402651</v>
       </c>
       <c r="AA19" t="n">
-        <v>96219.96970418221</v>
+        <v>96219.97440861558</v>
       </c>
       <c r="AB19" t="n">
-        <v>17438.0188081813</v>
+        <v>17438.01966076935</v>
       </c>
       <c r="AC19" t="n">
-        <v>410.2463615691958</v>
+        <v>410.2463816271591</v>
       </c>
       <c r="AD19" t="n">
-        <v>2254.223284917113</v>
+        <v>2254.223395131688</v>
       </c>
       <c r="AE19" t="n">
-        <v>7546.745219568159</v>
+        <v>7546.745588547278</v>
       </c>
       <c r="AF19" t="n">
-        <v>4125.292219100254</v>
+        <v>4125.292420796039</v>
       </c>
       <c r="AG19" t="n">
-        <v>36934.16298596717</v>
+        <v>36934.16479177013</v>
       </c>
       <c r="AH19" t="n">
-        <v>11901.15467034225</v>
+        <v>11901.15525221926</v>
       </c>
       <c r="AI19" t="n">
-        <v>27429.85647258503</v>
+        <v>27429.85781369885</v>
       </c>
       <c r="AJ19" t="n">
-        <v>10257.38208411169</v>
+        <v>10257.38258562058</v>
       </c>
       <c r="AK19" t="n">
-        <v>100520.0811278168</v>
+        <v>100520.0860424932</v>
       </c>
       <c r="AL19" t="n">
-        <v>219355.2090662016</v>
+        <v>219355.2197910227</v>
       </c>
       <c r="AM19" t="n">
-        <v>30612.16184772569</v>
+        <v>30612.16334443034</v>
       </c>
       <c r="AN19" t="n">
-        <v>27386.09016896827</v>
+        <v>27386.09150794225</v>
       </c>
       <c r="AO19" t="n">
-        <v>12210.73701375161</v>
+        <v>12210.73761076486</v>
       </c>
       <c r="AP19" t="n">
-        <v>14810.66549791594</v>
+        <v>14810.66622204615</v>
       </c>
       <c r="AQ19" t="n">
-        <v>34443.19219570834</v>
+        <v>34443.19387972156</v>
       </c>
       <c r="AR19" t="n">
-        <v>12754.00374269481</v>
+        <v>12754.00436626974</v>
       </c>
       <c r="AS19" t="n">
-        <v>10286.62837999316</v>
+        <v>10286.62888293197</v>
       </c>
       <c r="AT19" t="n">
-        <v>3747.094976326749</v>
+        <v>3747.095159531646</v>
       </c>
     </row>
     <row r="20">
@@ -2824,139 +2824,139 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>110334.4875106745</v>
+        <v>110334.4895417594</v>
       </c>
       <c r="C20" t="n">
-        <v>5691.227266508884</v>
+        <v>5691.22737982859</v>
       </c>
       <c r="D20" t="n">
-        <v>100650.7028390513</v>
+        <v>100650.7037393282</v>
       </c>
       <c r="E20" t="n">
-        <v>32456.02127663677</v>
+        <v>32456.02146067143</v>
       </c>
       <c r="F20" t="n">
-        <v>22473.3287285206</v>
+        <v>22473.32886445292</v>
       </c>
       <c r="G20" t="n">
-        <v>175336.116007759</v>
+        <v>175336.1202771734</v>
       </c>
       <c r="H20" t="n">
-        <v>9919.63145378001</v>
+        <v>9919.631684632865</v>
       </c>
       <c r="I20" t="n">
-        <v>26858.46756151594</v>
+        <v>26858.46776422882</v>
       </c>
       <c r="J20" t="n">
-        <v>40609.97580559005</v>
+        <v>40609.97637468755</v>
       </c>
       <c r="K20" t="n">
-        <v>69859.3694866218</v>
+        <v>69859.37074325926</v>
       </c>
       <c r="L20" t="n">
-        <v>47849.75127157864</v>
+        <v>47849.75189536886</v>
       </c>
       <c r="M20" t="n">
-        <v>14465.90282415055</v>
+        <v>14465.90302851665</v>
       </c>
       <c r="N20" t="n">
-        <v>31324.6282995366</v>
+        <v>31324.62869940202</v>
       </c>
       <c r="O20" t="n">
-        <v>21615.21876855899</v>
+        <v>21615.21901194838</v>
       </c>
       <c r="P20" t="n">
-        <v>59797.35999713039</v>
+        <v>59797.36027501243</v>
       </c>
       <c r="Q20" t="n">
-        <v>37619.62386685595</v>
+        <v>37619.62428679525</v>
       </c>
       <c r="R20" t="n">
-        <v>15298.92092897466</v>
+        <v>15298.92111486978</v>
       </c>
       <c r="S20" t="n">
-        <v>11907.8961755224</v>
+        <v>11907.89635206833</v>
       </c>
       <c r="T20" t="n">
-        <v>33906.31304101213</v>
+        <v>33906.31330603988</v>
       </c>
       <c r="U20" t="n">
-        <v>104008.4724263591</v>
+        <v>104008.4737392067</v>
       </c>
       <c r="V20" t="n">
-        <v>33768.33025476149</v>
+        <v>33768.33058765582</v>
       </c>
       <c r="W20" t="n">
-        <v>48451.45801094493</v>
+        <v>48451.45899523226</v>
       </c>
       <c r="X20" t="n">
-        <v>82608.88610490295</v>
+        <v>82608.8880433382</v>
       </c>
       <c r="Y20" t="n">
-        <v>22891.7289178737</v>
+        <v>22891.72939557932</v>
       </c>
       <c r="Z20" t="n">
-        <v>291262.5690111644</v>
+        <v>291262.570509085</v>
       </c>
       <c r="AA20" t="n">
-        <v>414704.1615867753</v>
+        <v>414704.1693603994</v>
       </c>
       <c r="AB20" t="n">
-        <v>109106.1055813702</v>
+        <v>109106.1073012019</v>
       </c>
       <c r="AC20" t="n">
-        <v>5935.665885960423</v>
+        <v>5935.665949665703</v>
       </c>
       <c r="AD20" t="n">
-        <v>23538.12704076388</v>
+        <v>23538.1273219852</v>
       </c>
       <c r="AE20" t="n">
-        <v>44986.28231468578</v>
+        <v>44986.28305115253</v>
       </c>
       <c r="AF20" t="n">
-        <v>18667.13700593514</v>
+        <v>18667.13737826834</v>
       </c>
       <c r="AG20" t="n">
-        <v>145133.2598049275</v>
+        <v>145133.2635919421</v>
       </c>
       <c r="AH20" t="n">
-        <v>55112.19894732081</v>
+        <v>55112.20017380582</v>
       </c>
       <c r="AI20" t="n">
-        <v>93537.43782578493</v>
+        <v>93537.44018850691</v>
       </c>
       <c r="AJ20" t="n">
-        <v>61126.59228562488</v>
+        <v>61126.59313981185</v>
       </c>
       <c r="AK20" t="n">
-        <v>380727.3589904523</v>
+        <v>380727.3679753464</v>
       </c>
       <c r="AL20" t="n">
-        <v>522370.9520801206</v>
+        <v>522370.9662468435</v>
       </c>
       <c r="AM20" t="n">
-        <v>150956.6013221141</v>
+        <v>150956.6037013705</v>
       </c>
       <c r="AN20" t="n">
-        <v>121900.1008145486</v>
+        <v>121900.1029812503</v>
       </c>
       <c r="AO20" t="n">
-        <v>209823.5484223097</v>
+        <v>209823.549502905</v>
       </c>
       <c r="AP20" t="n">
-        <v>120061.4435539704</v>
+        <v>120061.444464517</v>
       </c>
       <c r="AQ20" t="n">
-        <v>210747.5110652954</v>
+        <v>210747.513550692</v>
       </c>
       <c r="AR20" t="n">
-        <v>48550.11954952309</v>
+        <v>48550.12082599945</v>
       </c>
       <c r="AS20" t="n">
-        <v>50761.5707390273</v>
+        <v>50761.57168377072</v>
       </c>
       <c r="AT20" t="n">
-        <v>6310.49497632675</v>
+        <v>6310.495159531647</v>
       </c>
     </row>
   </sheetData>
